--- a/output/pdf_financials_xlsx/NCP.xlsx
+++ b/output/pdf_financials_xlsx/NCP.xlsx
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.38817</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-3.229693</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.164423</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -8799,7 +8799,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
         <v>-1.38817</v>
       </c>

--- a/output/pdf_financials_xlsx/NCP.xlsx
+++ b/output/pdf_financials_xlsx/NCP.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.010692</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.058022</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.055625</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.023112</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.012175</v>
       </c>
     </row>
     <row r="13">
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.755587</v>
+        <v>-1.766279</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.647473</v>
+        <v>-1.705495</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.494719</v>
+        <v>-3.550344</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.547923</v>
+        <v>-1.571035</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.405733</v>
+        <v>-1.417908</v>
       </c>
     </row>
     <row r="28">
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.574984</v>
+        <v>-1.585676</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.524681</v>
+        <v>-1.582703</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.381116</v>
+        <v>-3.436741</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.504297</v>
+        <v>-1.527409</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.367681</v>
+        <v>-1.379856</v>
       </c>
     </row>
     <row r="30">
@@ -3159,19 +3159,19 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.151045</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.098373</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.104818</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027205</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027945</v>
       </c>
     </row>
     <row r="125">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.151045</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.098373</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.104818</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027205</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027945</v>
       </c>
     </row>
     <row r="126">
@@ -6329,7 +6329,11 @@
           <t>Principal lease payments 8</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -7809,7 +7813,11 @@
           <t>Principal lease payments 10</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -9041,7 +9049,11 @@
           <t>Principal elements of lease payments</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>-0.151045</v>
       </c>
@@ -11456,7 +11468,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11497,7 +11509,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12455,7 +12467,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E222" s="5" t="n">

--- a/output/pdf_financials_xlsx/NCP.xlsx
+++ b/output/pdf_financials_xlsx/NCP.xlsx
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.09375</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.101617</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.025942</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
@@ -2006,13 +2006,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.09375</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.101617</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.025942</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>0</v>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.355415</v>
+        <v>0.261665</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.101617</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.025942</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>0.026649</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>0.109445</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0.017319</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>0.109445</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0.017319</v>
@@ -2203,16 +2203,14 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.006525400892505409</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.0138467922277593</v>
+        <v>0.09509106070793814</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-0.2204344099935866</v>
+        <v>-0.367670679311891</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>-0.07326231225986728</v>
@@ -2316,7 +2314,7 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>1.08586</v>
+        <v>0.976415</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0.9847939999999999</v>
@@ -2964,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.683378</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -5160,7 +5158,11 @@
           <t>Lease obligations 12</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5199,7 +5201,11 @@
           <t>Lease obligations 12</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -5566,7 +5572,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.09375</v>
       </c>
@@ -5605,7 +5615,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>0.109445</v>
       </c>
@@ -6247,7 +6261,11 @@
           <t>Proceeds from share issuances 10</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -7731,7 +7749,11 @@
           <t>Proceeds from share issuance 12</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -8848,7 +8870,11 @@
           <t>Proceeds on sale of marketable securities 7</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
